--- a/Result/profitability/1455.xlsx
+++ b/Result/profitability/1455.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.14625</v>
+        <v>-0.01250000000000004</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2149999999999997</v>
+        <v>1.41625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.12375</v>
+        <v>0.01249999999999996</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1837500000000004</v>
+        <v>2.14375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>-0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.11375</v>
+        <v>0.03374999999999996</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8187500000000003</v>
+        <v>2.735</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.39875</v>
+        <v>-0.23125</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.19375</v>
+        <v>-3.02</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3300000000000001</v>
+        <v>-0.20375</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.7925</v>
+        <v>-1.74375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,16 +1149,16 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.68</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.23875</v>
+        <v>-0.07750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0175</v>
+        <v>-0.2212499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,16 +1276,16 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.12125</v>
+        <v>0.004999999999999977</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5524999999999998</v>
+        <v>0.9225000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07375000000000004</v>
+        <v>-0.07375000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1337500000000003</v>
+        <v>0.1337500000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.53</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02000000000000005</v>
+        <v>-0.02</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7037500000000002</v>
+        <v>0.7037500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.51</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03499999999999996</v>
+        <v>0.03499999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>1.36125</v>
@@ -1899,7 +1899,7 @@
         <v>0.26</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07374999999999995</v>
+        <v>0.07374999999999998</v>
       </c>
       <c r="N12" t="n">
         <v>1.44125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1604</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E75" t="n">
+        <v>223</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="G75" t="n">
+        <v>124</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>419</v>
+      </c>
+      <c r="J75" t="n">
+        <v>542</v>
+      </c>
+      <c r="K75" t="n">
+        <v>512</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03875000000000003</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.9287500000000002</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>5.539906103286385</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.526315789473684</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-5.026011560693641</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
